--- a/backend/data/corpus/gold/gold_labeling.xlsx
+++ b/backend/data/corpus/gold/gold_labeling.xlsx
@@ -565,26 +565,14 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping sunk_cost_pressure (nothing paid yet) and reciprocity_hook (not a gift).</t>
-        </is>
-      </c>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -795,20 +783,12 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping payment_irreversibility — no payment mechanism in the text.</t>
-        </is>
-      </c>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -931,7 +911,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -944,11 +928,7 @@
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Consider adding isolation — 'stay on this call 24x7' matches that definition directly.</t>
-        </is>
-      </c>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1176,11 +1156,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
@@ -1191,18 +1167,14 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Judgment call: false_authority not clearly named; sunk_cost_pressure is weak (nothing paid yet) — maybe reciprocity_hook instead.</t>
-        </is>
-      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1303,32 +1275,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K22" s="3" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr"/>
       <c r="M22" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping payment_irreversibility and sunk_cost_pressure (nothing paid); fake_scarcity duplicates the urgency phrase.</t>
-        </is>
-      </c>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1415,7 +1371,11 @@
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -1423,22 +1383,18 @@
       </c>
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>Consider adding payment_irreversibility + manufactured_urgency (UPI collect request 'today'); verification_theater is weak here.</t>
-        </is>
-      </c>
+      <c r="P25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1737,11 +1693,7 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -1752,11 +1704,7 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping verification_theater — no fake proof shown, just a rate-plan ad.</t>
-        </is>
-      </c>
+      <c r="P34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1851,11 +1799,7 @@
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -1870,11 +1814,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping verification_theater — an 'identifier code' isn't fake proof.</t>
-        </is>
-      </c>
+      <c r="P37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2069,7 +2009,11 @@
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -2082,11 +2026,7 @@
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>Consider adding isolation — 'stay connected until officer confirms closure' is the same pattern as IN-004.</t>
-        </is>
-      </c>
+      <c r="P43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2145,11 +2085,7 @@
       <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -2158,11 +2094,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping payment_irreversibility — no payment mechanism visible (message is genuinely truncated in the source data).</t>
-        </is>
-      </c>
+      <c r="P45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2229,24 +2161,12 @@
           <t>x</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K47" s="3" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M47" s="3" t="inlineStr"/>
       <c r="N47" s="3" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping payment_irreversibility + reciprocity_hook — this message is the install-AnyDesk step, no payment/gift framing yet.</t>
-        </is>
-      </c>
+      <c r="P47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2303,11 +2223,7 @@
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -2322,11 +2238,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping verification_theater — no fake proof.</t>
-        </is>
-      </c>
+      <c r="P49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2345,7 +2257,11 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -2362,21 +2278,13 @@
       <c r="K50" s="3" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr"/>
       <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N50" s="3" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>Consider swapping fake_scarcity -&gt; manufactured_urgency ('today' is a deadline, not a slot count).</t>
-        </is>
-      </c>
+      <c r="P50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2395,25 +2303,17 @@
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr"/>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -2422,11 +2322,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping verification_theater + payment_irreversibility — premium-SMS prize spam, no fake proof or payment framing.</t>
-        </is>
-      </c>
+      <c r="P51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2581,38 +2477,30 @@
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr"/>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K56" s="3" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>Judgment call: payment_irreversibility is a stretch (direct transfer, not a receipt-framed trick); manufactured_urgency refers to refund timing, not an action deadline.</t>
-        </is>
-      </c>
+      <c r="P56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2737,17 +2625,9 @@
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr"/>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K60" s="3" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr"/>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -2756,11 +2636,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping verification_theater + payment_irreversibility.</t>
-        </is>
-      </c>
+      <c r="P60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2779,26 +2655,34 @@
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="3" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>Consider adding verification_theater — 'FIR copy and ID card' is the definition's own example.</t>
-        </is>
-      </c>
+      <c r="P61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2988,19 +2872,15 @@
       </c>
       <c r="D67" s="3" t="inlineStr"/>
       <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr"/>
       <c r="M67" s="3" t="inlineStr">
@@ -3010,11 +2890,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr"/>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>Consider dropping verification_theater + channel_switch — sharing to groups isn't channel_switch; no fake proof.</t>
-        </is>
-      </c>
+      <c r="P67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3066,7 +2942,11 @@
           <t>Dear Customer, Rs 4,999.00 has been debited from your account ending 4521 on 02-Aug-26 towards UPI/DebitCard txn at Big Bazaar. Avl bal Rs 12,340.50.</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr"/>
@@ -3128,9 +3008,21 @@
       </c>
       <c r="D71" s="3" t="inlineStr"/>
       <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I71" s="3" t="inlineStr"/>
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr"/>
@@ -3217,7 +3109,11 @@
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
-      <c r="E74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr"/>
       <c r="H74" s="3" t="inlineStr"/>
@@ -3225,7 +3121,11 @@
       <c r="J74" s="3" t="inlineStr"/>
       <c r="K74" s="3" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr"/>
-      <c r="M74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N74" s="3" t="inlineStr"/>
       <c r="O74" s="3" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr"/>
@@ -3255,7 +3155,11 @@
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="3" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr"/>
-      <c r="M75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr"/>
       <c r="P75" s="2" t="inlineStr"/>
@@ -3336,7 +3240,11 @@
           <t>Your Swiggy order #4521 has been picked up and is on the way. Estimated delivery in 22 minutes. Track live at swiggy.com/track</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr"/>
@@ -3427,7 +3335,11 @@
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
-      <c r="E81" s="3" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr"/>
@@ -3435,7 +3347,11 @@
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr"/>
       <c r="L81" s="3" t="inlineStr"/>
-      <c r="M81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N81" s="3" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr"/>
@@ -3488,9 +3404,21 @@
       </c>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr"/>
@@ -3547,15 +3475,27 @@
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr"/>
-      <c r="E85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="3" t="inlineStr"/>
       <c r="H85" s="3" t="inlineStr"/>
       <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr"/>
-      <c r="K85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L85" s="3" t="inlineStr"/>
-      <c r="M85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N85" s="3" t="inlineStr"/>
       <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr"/>
@@ -3607,7 +3547,11 @@
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="3" t="inlineStr"/>
@@ -3615,7 +3559,11 @@
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="3" t="inlineStr"/>
       <c r="L87" s="3" t="inlineStr"/>
-      <c r="M87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N87" s="3" t="inlineStr"/>
       <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr"/>
@@ -3668,9 +3616,21 @@
       </c>
       <c r="D89" s="3" t="inlineStr"/>
       <c r="E89" s="3" t="inlineStr"/>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr"/>
       <c r="K89" s="3" t="inlineStr"/>
@@ -3698,9 +3658,21 @@
       </c>
       <c r="D90" s="3" t="inlineStr"/>
       <c r="E90" s="3" t="inlineStr"/>
-      <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
-      <c r="H90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr"/>
       <c r="K90" s="3" t="inlineStr"/>
@@ -3817,14 +3789,26 @@
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" s="3" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H94" s="3" t="inlineStr"/>
       <c r="I94" s="3" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr"/>
       <c r="K94" s="3" t="inlineStr"/>
-      <c r="L94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="3" t="inlineStr"/>
@@ -3876,7 +3860,11 @@
           <t>BangBabes Ur order is on the way. U SHOULD receive a Service Msg 2 download UR content. If U do not, GoTo wap. bangb. tv on UR mobile internet/service menu</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E96" s="3" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr"/>
       <c r="G96" s="3" t="inlineStr"/>
@@ -3937,17 +3925,33 @@
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="3" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G98" s="3" t="inlineStr"/>
-      <c r="H98" s="3" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I98" s="3" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr"/>
       <c r="K98" s="3" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr"/>
       <c r="M98" s="3" t="inlineStr"/>
       <c r="N98" s="3" t="inlineStr"/>
-      <c r="O98" s="3" t="inlineStr"/>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
@@ -4208,10 +4212,18 @@
       </c>
       <c r="D107" s="3" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G107" s="3" t="inlineStr"/>
       <c r="H107" s="3" t="inlineStr"/>
-      <c r="I107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="3" t="inlineStr"/>
       <c r="L107" s="3" t="inlineStr"/>
@@ -4326,7 +4338,11 @@
           <t>Reminder: Your appointment with Dr. Mehta at Apollo Clinic is scheduled for tomorrow at 11:00 AM. Reply CONFIRM or CANCEL.</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr"/>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr"/>
       <c r="G111" s="3" t="inlineStr"/>
@@ -4515,7 +4531,11 @@
       <c r="J117" s="3" t="inlineStr"/>
       <c r="K117" s="3" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr"/>
-      <c r="M117" s="3" t="inlineStr"/>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N117" s="3" t="inlineStr"/>
       <c r="O117" s="3" t="inlineStr"/>
       <c r="P117" s="2" t="inlineStr"/>
@@ -4597,8 +4617,16 @@
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr"/>
-      <c r="E120" s="3" t="inlineStr"/>
-      <c r="F120" s="3" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="3" t="inlineStr"/>
       <c r="I120" s="3" t="inlineStr"/>
@@ -4606,7 +4634,11 @@
       <c r="K120" s="3" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr"/>
       <c r="M120" s="3" t="inlineStr"/>
-      <c r="N120" s="3" t="inlineStr"/>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O120" s="3" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr"/>
     </row>
@@ -4785,7 +4817,11 @@
       <c r="J126" s="3" t="inlineStr"/>
       <c r="K126" s="3" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr"/>
-      <c r="M126" s="3" t="inlineStr"/>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N126" s="3" t="inlineStr"/>
       <c r="O126" s="3" t="inlineStr"/>
       <c r="P126" s="2" t="inlineStr"/>
@@ -4867,7 +4903,11 @@
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
-      <c r="E129" s="3" t="inlineStr"/>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F129" s="3" t="inlineStr"/>
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr"/>
@@ -4875,7 +4915,11 @@
       <c r="J129" s="3" t="inlineStr"/>
       <c r="K129" s="3" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
-      <c r="M129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N129" s="3" t="inlineStr"/>
       <c r="O129" s="3" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr"/>
@@ -5107,10 +5151,22 @@
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr"/>
-      <c r="E137" s="3" t="inlineStr"/>
-      <c r="F137" s="3" t="inlineStr"/>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G137" s="3" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I137" s="3" t="inlineStr"/>
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="3" t="inlineStr"/>
@@ -5286,7 +5342,11 @@
           <t>Reminder from your bank: never share your card PIN, CVV, or OTP with anyone over phone or email, including people claiming to be bank employees.</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr"/>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr"/>
       <c r="G143" s="3" t="inlineStr"/>
@@ -5317,14 +5377,26 @@
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr"/>
-      <c r="E144" s="3" t="inlineStr"/>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F144" s="3" t="inlineStr"/>
       <c r="G144" s="3" t="inlineStr"/>
       <c r="H144" s="3" t="inlineStr"/>
       <c r="I144" s="3" t="inlineStr"/>
-      <c r="J144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="K144" s="3" t="inlineStr"/>
-      <c r="L144" s="3" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M144" s="3" t="inlineStr"/>
       <c r="N144" s="3" t="inlineStr"/>
       <c r="O144" s="3" t="inlineStr"/>
@@ -5498,12 +5570,24 @@
       </c>
       <c r="D150" s="3" t="inlineStr"/>
       <c r="E150" s="3" t="inlineStr"/>
-      <c r="F150" s="3" t="inlineStr"/>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G150" s="3" t="inlineStr"/>
-      <c r="H150" s="3" t="inlineStr"/>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I150" s="3" t="inlineStr"/>
       <c r="J150" s="3" t="inlineStr"/>
-      <c r="K150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L150" s="3" t="inlineStr"/>
       <c r="M150" s="3" t="inlineStr"/>
       <c r="N150" s="3" t="inlineStr"/>
@@ -5654,7 +5738,11 @@
       <c r="I155" s="3" t="inlineStr"/>
       <c r="J155" s="3" t="inlineStr"/>
       <c r="K155" s="3" t="inlineStr"/>
-      <c r="L155" s="3" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M155" s="3" t="inlineStr"/>
       <c r="N155" s="3" t="inlineStr"/>
       <c r="O155" s="3" t="inlineStr"/>
@@ -5766,7 +5854,11 @@
           <t>"For the most sparkling shopping breaks from 45 per person; call 0121 2025050 or visit www.shortbreaks.org.uk"</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr"/>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr"/>
       <c r="G159" s="3" t="inlineStr"/>
@@ -5798,10 +5890,26 @@
       </c>
       <c r="D160" s="3" t="inlineStr"/>
       <c r="E160" s="3" t="inlineStr"/>
-      <c r="F160" s="3" t="inlineStr"/>
-      <c r="G160" s="3" t="inlineStr"/>
-      <c r="H160" s="3" t="inlineStr"/>
-      <c r="I160" s="3" t="inlineStr"/>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J160" s="3" t="inlineStr"/>
       <c r="K160" s="3" t="inlineStr"/>
       <c r="L160" s="3" t="inlineStr"/>
@@ -5857,15 +5965,27 @@
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr"/>
-      <c r="E162" s="3" t="inlineStr"/>
-      <c r="F162" s="3" t="inlineStr"/>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G162" s="3" t="inlineStr"/>
       <c r="H162" s="3" t="inlineStr"/>
       <c r="I162" s="3" t="inlineStr"/>
       <c r="J162" s="3" t="inlineStr"/>
       <c r="K162" s="3" t="inlineStr"/>
       <c r="L162" s="3" t="inlineStr"/>
-      <c r="M162" s="3" t="inlineStr"/>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N162" s="3" t="inlineStr"/>
       <c r="O162" s="3" t="inlineStr"/>
       <c r="P162" s="2" t="inlineStr"/>
@@ -5916,7 +6036,11 @@
           <t>Zomato Gold membership renews on 10-Aug-26 for Rs 149. Manage your subscription anytime in the app under Account Settings.</t>
         </is>
       </c>
-      <c r="D164" s="3" t="inlineStr"/>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E164" s="3" t="inlineStr"/>
       <c r="F164" s="3" t="inlineStr"/>
       <c r="G164" s="3" t="inlineStr"/>
@@ -6007,7 +6131,11 @@
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr"/>
-      <c r="E167" s="3" t="inlineStr"/>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F167" s="3" t="inlineStr"/>
       <c r="G167" s="3" t="inlineStr"/>
       <c r="H167" s="3" t="inlineStr"/>
@@ -6015,7 +6143,11 @@
       <c r="J167" s="3" t="inlineStr"/>
       <c r="K167" s="3" t="inlineStr"/>
       <c r="L167" s="3" t="inlineStr"/>
-      <c r="M167" s="3" t="inlineStr"/>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N167" s="3" t="inlineStr"/>
       <c r="O167" s="3" t="inlineStr"/>
       <c r="P167" s="2" t="inlineStr"/>
@@ -6188,10 +6320,22 @@
       </c>
       <c r="D173" s="3" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr"/>
-      <c r="F173" s="3" t="inlineStr"/>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G173" s="3" t="inlineStr"/>
-      <c r="H173" s="3" t="inlineStr"/>
-      <c r="I173" s="3" t="inlineStr"/>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J173" s="3" t="inlineStr"/>
       <c r="K173" s="3" t="inlineStr"/>
       <c r="L173" s="3" t="inlineStr"/>
@@ -6306,7 +6450,11 @@
           <t>Namaste, this is a reminder to renew your vehicle insurance before it expires on 30-Aug-26 to stay covered and compliant.</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr"/>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E177" s="3" t="inlineStr"/>
       <c r="F177" s="3" t="inlineStr"/>
       <c r="G177" s="3" t="inlineStr"/>
@@ -6397,10 +6545,22 @@
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr"/>
-      <c r="E180" s="3" t="inlineStr"/>
-      <c r="F180" s="3" t="inlineStr"/>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G180" s="3" t="inlineStr"/>
-      <c r="H180" s="3" t="inlineStr"/>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I180" s="3" t="inlineStr"/>
       <c r="J180" s="3" t="inlineStr"/>
       <c r="K180" s="3" t="inlineStr"/>
@@ -6426,7 +6586,11 @@
           <t>RBI has released updated guidelines advising customers to never share their UPI PIN or OTP with anyone, including bank staff. Stay safe.</t>
         </is>
       </c>
-      <c r="D181" s="3" t="inlineStr"/>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3" t="inlineStr"/>
       <c r="G181" s="3" t="inlineStr"/>
@@ -6465,7 +6629,11 @@
       <c r="J182" s="3" t="inlineStr"/>
       <c r="K182" s="3" t="inlineStr"/>
       <c r="L182" s="3" t="inlineStr"/>
-      <c r="M182" s="3" t="inlineStr"/>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N182" s="3" t="inlineStr"/>
       <c r="O182" s="3" t="inlineStr"/>
       <c r="P182" s="2" t="inlineStr"/>
@@ -6637,7 +6805,11 @@
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr"/>
-      <c r="E188" s="3" t="inlineStr"/>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F188" s="3" t="inlineStr"/>
       <c r="G188" s="3" t="inlineStr"/>
       <c r="H188" s="3" t="inlineStr"/>
@@ -6645,9 +6817,17 @@
       <c r="J188" s="3" t="inlineStr"/>
       <c r="K188" s="3" t="inlineStr"/>
       <c r="L188" s="3" t="inlineStr"/>
-      <c r="M188" s="3" t="inlineStr"/>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N188" s="3" t="inlineStr"/>
-      <c r="O188" s="3" t="inlineStr"/>
+      <c r="O188" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
@@ -6698,9 +6878,21 @@
       </c>
       <c r="D190" s="3" t="inlineStr"/>
       <c r="E190" s="3" t="inlineStr"/>
-      <c r="F190" s="3" t="inlineStr"/>
-      <c r="G190" s="3" t="inlineStr"/>
-      <c r="H190" s="3" t="inlineStr"/>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I190" s="3" t="inlineStr"/>
       <c r="J190" s="3" t="inlineStr"/>
       <c r="K190" s="3" t="inlineStr"/>
@@ -6765,7 +6957,11 @@
       <c r="J192" s="3" t="inlineStr"/>
       <c r="K192" s="3" t="inlineStr"/>
       <c r="L192" s="3" t="inlineStr"/>
-      <c r="M192" s="3" t="inlineStr"/>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N192" s="3" t="inlineStr"/>
       <c r="O192" s="3" t="inlineStr"/>
       <c r="P192" s="2" t="inlineStr"/>
@@ -6786,7 +6982,11 @@
           <t>88066 FROM 88066 LOST 3POUND HELP</t>
         </is>
       </c>
-      <c r="D193" s="3" t="inlineStr"/>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3" t="inlineStr"/>
       <c r="G193" s="3" t="inlineStr"/>
@@ -6818,11 +7018,19 @@
       </c>
       <c r="D194" s="3" t="inlineStr"/>
       <c r="E194" s="3" t="inlineStr"/>
-      <c r="F194" s="3" t="inlineStr"/>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G194" s="3" t="inlineStr"/>
       <c r="H194" s="3" t="inlineStr"/>
       <c r="I194" s="3" t="inlineStr"/>
-      <c r="J194" s="3" t="inlineStr"/>
+      <c r="J194" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="K194" s="3" t="inlineStr"/>
       <c r="L194" s="3" t="inlineStr"/>
       <c r="M194" s="3" t="inlineStr"/>
@@ -6882,7 +7090,11 @@
       <c r="G196" s="3" t="inlineStr"/>
       <c r="H196" s="3" t="inlineStr"/>
       <c r="I196" s="3" t="inlineStr"/>
-      <c r="J196" s="3" t="inlineStr"/>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="K196" s="3" t="inlineStr"/>
       <c r="L196" s="3" t="inlineStr"/>
       <c r="M196" s="3" t="inlineStr"/>
@@ -6937,7 +7149,11 @@
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr"/>
-      <c r="E198" s="3" t="inlineStr"/>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F198" s="3" t="inlineStr"/>
       <c r="G198" s="3" t="inlineStr"/>
       <c r="H198" s="3" t="inlineStr"/>
@@ -6945,8 +7161,16 @@
       <c r="J198" s="3" t="inlineStr"/>
       <c r="K198" s="3" t="inlineStr"/>
       <c r="L198" s="3" t="inlineStr"/>
-      <c r="M198" s="3" t="inlineStr"/>
-      <c r="N198" s="3" t="inlineStr"/>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O198" s="3" t="inlineStr"/>
       <c r="P198" s="2" t="inlineStr"/>
     </row>
@@ -6967,11 +7191,27 @@
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
-      <c r="E199" s="3" t="inlineStr"/>
-      <c r="F199" s="3" t="inlineStr"/>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G199" s="3" t="inlineStr"/>
-      <c r="H199" s="3" t="inlineStr"/>
-      <c r="I199" s="3" t="inlineStr"/>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J199" s="3" t="inlineStr"/>
       <c r="K199" s="3" t="inlineStr"/>
       <c r="L199" s="3" t="inlineStr"/>
@@ -7027,7 +7267,11 @@
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr"/>
-      <c r="E201" s="3" t="inlineStr"/>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F201" s="3" t="inlineStr"/>
       <c r="G201" s="3" t="inlineStr"/>
       <c r="H201" s="3" t="inlineStr"/>
@@ -7035,7 +7279,11 @@
       <c r="J201" s="3" t="inlineStr"/>
       <c r="K201" s="3" t="inlineStr"/>
       <c r="L201" s="3" t="inlineStr"/>
-      <c r="M201" s="3" t="inlineStr"/>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N201" s="3" t="inlineStr"/>
       <c r="O201" s="3" t="inlineStr"/>
       <c r="P201" s="2" t="inlineStr"/>
@@ -7177,8 +7425,16 @@
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr"/>
-      <c r="E206" s="3" t="inlineStr"/>
-      <c r="F206" s="3" t="inlineStr"/>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G206" s="3" t="inlineStr"/>
       <c r="H206" s="3" t="inlineStr"/>
       <c r="I206" s="3" t="inlineStr"/>
@@ -7186,7 +7442,11 @@
       <c r="K206" s="3" t="inlineStr"/>
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
-      <c r="N206" s="3" t="inlineStr"/>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O206" s="3" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr"/>
     </row>
@@ -7245,7 +7505,11 @@
       <c r="J208" s="3" t="inlineStr"/>
       <c r="K208" s="3" t="inlineStr"/>
       <c r="L208" s="3" t="inlineStr"/>
-      <c r="M208" s="3" t="inlineStr"/>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N208" s="3" t="inlineStr"/>
       <c r="O208" s="3" t="inlineStr"/>
       <c r="P208" s="2" t="inlineStr"/>
@@ -7328,11 +7592,19 @@
       </c>
       <c r="D211" s="3" t="inlineStr"/>
       <c r="E211" s="3" t="inlineStr"/>
-      <c r="F211" s="3" t="inlineStr"/>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G211" s="3" t="inlineStr"/>
       <c r="H211" s="3" t="inlineStr"/>
       <c r="I211" s="3" t="inlineStr"/>
-      <c r="J211" s="3" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="K211" s="3" t="inlineStr"/>
       <c r="L211" s="3" t="inlineStr"/>
       <c r="M211" s="3" t="inlineStr"/>
@@ -7417,12 +7689,28 @@
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr"/>
-      <c r="E214" s="3" t="inlineStr"/>
-      <c r="F214" s="3" t="inlineStr"/>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G214" s="3" t="inlineStr"/>
-      <c r="H214" s="3" t="inlineStr"/>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I214" s="3" t="inlineStr"/>
-      <c r="J214" s="3" t="inlineStr"/>
+      <c r="J214" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="K214" s="3" t="inlineStr"/>
       <c r="L214" s="3" t="inlineStr"/>
       <c r="M214" s="3" t="inlineStr"/>
@@ -7746,7 +8034,11 @@
           <t>Your electricity bill of Rs 1,240 for July is due on 15-Aug-26. Pay via the official BESCOM app or website to avoid a late fee.</t>
         </is>
       </c>
-      <c r="D225" s="3" t="inlineStr"/>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E225" s="3" t="inlineStr"/>
       <c r="F225" s="3" t="inlineStr"/>
       <c r="G225" s="3" t="inlineStr"/>
@@ -7896,7 +8188,11 @@
           <t>Thank you for shopping with us. Your Myntra return has been approved and Rs 1,299 will be refunded to your original payment method in 5-7 business days.</t>
         </is>
       </c>
-      <c r="D230" s="3" t="inlineStr"/>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E230" s="3" t="inlineStr"/>
       <c r="F230" s="3" t="inlineStr"/>
       <c r="G230" s="3" t="inlineStr"/>
@@ -7926,7 +8222,11 @@
           <t>Your flight 6E-2041 to Bengaluru on 14-Aug-26 is confirmed. Web check-in opens 48 hours before departure.</t>
         </is>
       </c>
-      <c r="D231" s="3" t="inlineStr"/>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E231" s="3" t="inlineStr"/>
       <c r="F231" s="3" t="inlineStr"/>
       <c r="G231" s="3" t="inlineStr"/>
@@ -7958,9 +8258,21 @@
       </c>
       <c r="D232" s="3" t="inlineStr"/>
       <c r="E232" s="3" t="inlineStr"/>
-      <c r="F232" s="3" t="inlineStr"/>
-      <c r="G232" s="3" t="inlineStr"/>
-      <c r="H232" s="3" t="inlineStr"/>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I232" s="3" t="inlineStr"/>
       <c r="J232" s="3" t="inlineStr"/>
       <c r="K232" s="3" t="inlineStr"/>
@@ -7987,9 +8299,21 @@
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr"/>
-      <c r="E233" s="3" t="inlineStr"/>
-      <c r="F233" s="3" t="inlineStr"/>
-      <c r="G233" s="3" t="inlineStr"/>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H233" s="3" t="inlineStr"/>
       <c r="I233" s="3" t="inlineStr"/>
       <c r="J233" s="3" t="inlineStr"/>
@@ -8017,10 +8341,22 @@
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr"/>
-      <c r="E234" s="3" t="inlineStr"/>
-      <c r="F234" s="3" t="inlineStr"/>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G234" s="3" t="inlineStr"/>
-      <c r="H234" s="3" t="inlineStr"/>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I234" s="3" t="inlineStr"/>
       <c r="J234" s="3" t="inlineStr"/>
       <c r="K234" s="3" t="inlineStr"/>
@@ -8107,10 +8443,22 @@
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr"/>
-      <c r="E237" s="3" t="inlineStr"/>
-      <c r="F237" s="3" t="inlineStr"/>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G237" s="3" t="inlineStr"/>
-      <c r="H237" s="3" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I237" s="3" t="inlineStr"/>
       <c r="J237" s="3" t="inlineStr"/>
       <c r="K237" s="3" t="inlineStr"/>
@@ -8226,7 +8574,11 @@
           <t>Sorry! U can not unsubscribe yet. THE MOB offer package has a min term of 54 weeks&gt; pls resubmit request after expiry. Reply THEMOB HELP 4 more info</t>
         </is>
       </c>
-      <c r="D241" s="3" t="inlineStr"/>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E241" s="3" t="inlineStr"/>
       <c r="F241" s="3" t="inlineStr"/>
       <c r="G241" s="3" t="inlineStr"/>
@@ -8257,7 +8609,11 @@
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
-      <c r="E242" s="3" t="inlineStr"/>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F242" s="3" t="inlineStr"/>
       <c r="G242" s="3" t="inlineStr"/>
       <c r="H242" s="3" t="inlineStr"/>
@@ -8265,8 +8621,16 @@
       <c r="J242" s="3" t="inlineStr"/>
       <c r="K242" s="3" t="inlineStr"/>
       <c r="L242" s="3" t="inlineStr"/>
-      <c r="M242" s="3" t="inlineStr"/>
-      <c r="N242" s="3" t="inlineStr"/>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O242" s="3" t="inlineStr"/>
       <c r="P242" s="2" t="inlineStr"/>
     </row>
@@ -8317,8 +8681,16 @@
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr"/>
-      <c r="E244" s="3" t="inlineStr"/>
-      <c r="F244" s="3" t="inlineStr"/>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G244" s="3" t="inlineStr"/>
       <c r="H244" s="3" t="inlineStr"/>
       <c r="I244" s="3" t="inlineStr"/>
@@ -8346,7 +8718,11 @@
           <t>Your credit card statement for card ending 7788 is generated. Total due Rs 8,420. Minimum due Rs 850. Due date 20-Aug-26.</t>
         </is>
       </c>
-      <c r="D245" s="3" t="inlineStr"/>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E245" s="3" t="inlineStr"/>
       <c r="F245" s="3" t="inlineStr"/>
       <c r="G245" s="3" t="inlineStr"/>
@@ -8467,10 +8843,22 @@
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr"/>
-      <c r="E249" s="3" t="inlineStr"/>
-      <c r="F249" s="3" t="inlineStr"/>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G249" s="3" t="inlineStr"/>
-      <c r="H249" s="3" t="inlineStr"/>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I249" s="3" t="inlineStr"/>
       <c r="J249" s="3" t="inlineStr"/>
       <c r="K249" s="3" t="inlineStr"/>
@@ -8497,10 +8885,22 @@
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr"/>
-      <c r="E250" s="3" t="inlineStr"/>
-      <c r="F250" s="3" t="inlineStr"/>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G250" s="3" t="inlineStr"/>
-      <c r="H250" s="3" t="inlineStr"/>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I250" s="3" t="inlineStr"/>
       <c r="J250" s="3" t="inlineStr"/>
       <c r="K250" s="3" t="inlineStr"/>

--- a/backend/data/corpus/gold/gold_labeling.xlsx
+++ b/backend/data/corpus/gold/gold_labeling.xlsx
@@ -840,7 +840,11 @@
           <t>Oi. Ami parchi na re. Kicchu kaaj korte iccha korche na. Phone ta tul na. Plz. Plz.</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr"/>
@@ -2976,7 +2980,11 @@
           <t>Bognor it is! Should be splendid at this time of year.</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E70" s="3" t="inlineStr"/>
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr"/>
@@ -3048,7 +3056,11 @@
           <t>My friend, she's studying at warwick, we've planned to go shopping and to concert tmw, but it may be canceled, havn't seen  for ages, yeah we should get together sometime!</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr"/>
@@ -3078,7 +3090,11 @@
           <t>Lol ok your forgiven :)</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr"/>
@@ -3180,7 +3196,11 @@
           <t>Ü dun need to pick ur gf?</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E76" s="3" t="inlineStr"/>
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr"/>
@@ -3210,7 +3230,11 @@
           <t>Yeah just open chat and click friend lists. Then make the list. Easy as pie</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E77" s="3" t="inlineStr"/>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr"/>
@@ -3274,7 +3298,11 @@
           <t>Change windows logoff sound..</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr"/>
@@ -3304,7 +3332,11 @@
           <t>Noooooooo please. Last thing I need is stress. For once in your life be fair.</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="inlineStr"/>
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" s="3" t="inlineStr"/>
@@ -3372,7 +3404,11 @@
           <t>Omg it could snow here tonite!</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E82" s="3" t="inlineStr"/>
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr"/>
@@ -3444,7 +3480,11 @@
           <t>Then get some cash together and I'll text jason</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E84" s="3" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr"/>
@@ -3516,7 +3556,11 @@
           <t>What makes you most happy?</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E86" s="3" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" s="3" t="inlineStr"/>
@@ -3584,7 +3628,11 @@
           <t>Ya ok, then had dinner?</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr"/>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E88" s="3" t="inlineStr"/>
       <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr"/>
@@ -3698,7 +3746,11 @@
           <t>I am taking you for italian food. How about a pretty dress with no panties? :)</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr"/>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3" t="inlineStr"/>
       <c r="G91" s="3" t="inlineStr"/>
@@ -3728,7 +3780,11 @@
           <t>For many things its an antibiotic and it can be used for chest abdomen and gynae infections even bone infections.</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E92" s="3" t="inlineStr"/>
       <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" s="3" t="inlineStr"/>
@@ -3758,7 +3814,11 @@
           <t>Ha! I wouldn't say that I just didn't read anything into way u seemed. I don't like 2 be judgemental....i save that for fridays in the pub!</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr"/>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E93" s="3" t="inlineStr"/>
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr"/>
@@ -3830,7 +3890,11 @@
           <t>I am in bus on the way to calicut</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr"/>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" s="3" t="inlineStr"/>
@@ -3894,7 +3958,11 @@
           <t>Yes see ya not on the dot</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr"/>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E97" s="3" t="inlineStr"/>
       <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" s="3" t="inlineStr"/>
@@ -3970,7 +4038,11 @@
           <t>Ü still attending da talks?</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" s="3" t="inlineStr"/>
@@ -4000,7 +4072,11 @@
           <t>Oh...i asked for fun. Haha...take care. ü</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr"/>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E100" s="3" t="inlineStr"/>
       <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" s="3" t="inlineStr"/>
@@ -4030,7 +4106,11 @@
           <t>I'm gonna be home soon and i don't want to talk about this stuff anymore tonight, k? I've cried enough today.</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr"/>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr"/>
       <c r="G101" s="3" t="inlineStr"/>
@@ -4060,7 +4140,11 @@
           <t>Sounds great! Im going to sleep now. Have a good night!</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr"/>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E102" s="3" t="inlineStr"/>
       <c r="F102" s="3" t="inlineStr"/>
       <c r="G102" s="3" t="inlineStr"/>
@@ -4090,7 +4174,11 @@
           <t>All day working day:)except saturday and sunday..</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr"/>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" s="3" t="inlineStr"/>
@@ -4120,7 +4208,11 @@
           <t>Ü v ma fan...</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E104" s="3" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr"/>
       <c r="G104" s="3" t="inlineStr"/>
@@ -4150,7 +4242,11 @@
           <t>Man this bus is so so so slow. I think you're gonna get there before me</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr"/>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr"/>
@@ -4180,7 +4276,11 @@
           <t>Hi its in durban are you still on this number</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr"/>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E106" s="3" t="inlineStr"/>
       <c r="F106" s="3" t="inlineStr"/>
       <c r="G106" s="3" t="inlineStr"/>
@@ -4248,7 +4348,11 @@
           <t>Yeah, where's your class at?</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr"/>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E108" s="3" t="inlineStr"/>
       <c r="F108" s="3" t="inlineStr"/>
       <c r="G108" s="3" t="inlineStr"/>
@@ -4278,7 +4382,11 @@
           <t>idc get over here, you are not weaseling your way out of this shit twice in a row</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr"/>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr"/>
       <c r="G109" s="3" t="inlineStr"/>
@@ -4308,7 +4416,11 @@
           <t xml:space="preserve">You stayin out of trouble stranger!!saw Dave the other day hes sorted now!still with me bloke when u gona get a girl MR!ur mum still Thinks we will get 2GETHA! </t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3" t="inlineStr"/>
       <c r="G110" s="3" t="inlineStr"/>
@@ -4372,7 +4484,11 @@
           <t>Do u still have plumbers tape and a wrench we could borrow?</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E112" s="3" t="inlineStr"/>
       <c r="F112" s="3" t="inlineStr"/>
       <c r="G112" s="3" t="inlineStr"/>
@@ -4402,7 +4518,11 @@
           <t xml:space="preserve">Goodo! Yes we must speak friday - egg-potato ratio for tortilla needed! </t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr"/>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr"/>
       <c r="G113" s="3" t="inlineStr"/>
@@ -4432,7 +4552,11 @@
           <t>It's wylie, you in tampa or sarasota?</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr"/>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E114" s="3" t="inlineStr"/>
       <c r="F114" s="3" t="inlineStr"/>
       <c r="G114" s="3" t="inlineStr"/>
@@ -4462,7 +4586,11 @@
           <t>I got a call from a landline number. . . I am asked to come to anna nagar . . . I will go in the afternoon</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr"/>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr"/>
       <c r="G115" s="3" t="inlineStr"/>
@@ -4492,7 +4620,11 @@
           <t>Jus ans me lar. U'll noe later.</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr"/>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E116" s="3" t="inlineStr"/>
       <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" s="3" t="inlineStr"/>
@@ -4556,7 +4688,11 @@
           <t>We are hoping to get away by 7, from Langport. You still up for town tonight?</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr"/>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E118" s="3" t="inlineStr"/>
       <c r="F118" s="3" t="inlineStr"/>
       <c r="G118" s="3" t="inlineStr"/>
@@ -4586,7 +4722,11 @@
           <t>WHEN THE FIRST STRIKE IS A RED ONE. THE BIRD + ANTELOPE BEGIN TOPLAY IN THE FIELDOF SELFINDEPENDENCE BELIEVE THIS + THE FLOWER OF CONTENTION WILL GROW.RANDOM!</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr"/>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E119" s="3" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr"/>
       <c r="G119" s="3" t="inlineStr"/>
@@ -4658,7 +4798,11 @@
           <t>He is there. You call and meet him</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr"/>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr"/>
       <c r="G121" s="3" t="inlineStr"/>
@@ -4688,7 +4832,11 @@
           <t>It took Mr owl 3 licks</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3" t="inlineStr"/>
       <c r="G122" s="3" t="inlineStr"/>
@@ -4718,7 +4866,11 @@
           <t>No we put party 7 days a week and study lightly, I think we need to draw in some custom checkboxes so they know we're hardcore</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr"/>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3" t="inlineStr"/>
       <c r="G123" s="3" t="inlineStr"/>
@@ -4748,7 +4900,11 @@
           <t>GOD ASKED, "What is forgiveness?" A little child gave lovely reply, "It is d wonderful fruit that a tree gives when it is being hurt by a stone.. Good night......</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr"/>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E124" s="3" t="inlineStr"/>
       <c r="F124" s="3" t="inlineStr"/>
       <c r="G124" s="3" t="inlineStr"/>
@@ -4778,7 +4934,11 @@
           <t>Pls help me tell Ashley that i cant find her number oh</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr"/>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr"/>
       <c r="G125" s="3" t="inlineStr"/>
@@ -4842,7 +5002,11 @@
           <t>:-) yeah! Lol. Luckily i didn't have a starring role like you!</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr"/>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr"/>
@@ -4872,7 +5036,11 @@
           <t>In e msg jus now. U said thanks for gift.</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr"/>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E128" s="3" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr"/>
       <c r="G128" s="3" t="inlineStr"/>
@@ -4940,7 +5108,11 @@
           <t>Good afternon, my love. How are today? I hope your good and maybe have some interviews. I wake and miss you babe. A passionate kiss from across the sea</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr"/>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3" t="inlineStr"/>
       <c r="G130" s="3" t="inlineStr"/>
@@ -4970,7 +5142,11 @@
           <t>That's cause your old. I live to be high.</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr"/>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr"/>
       <c r="G131" s="3" t="inlineStr"/>
@@ -5000,7 +5176,11 @@
           <t>Just sing HU. I think its also important to find someone female that know the place well preferably a citizen that is also smart to help you navigate through. Even things like choosing a phone plan require guidance. When in doubt ask especially girls.</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr"/>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E132" s="3" t="inlineStr"/>
       <c r="F132" s="3" t="inlineStr"/>
       <c r="G132" s="3" t="inlineStr"/>
@@ -5030,7 +5210,11 @@
           <t>S'fine. Anytime. All the best with it.</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr"/>
       <c r="G133" s="3" t="inlineStr"/>
@@ -5060,7 +5244,11 @@
           <t>Eek that's a lot of time especially since American Pie is like 8 minutes long. I can't stop singing it.</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr"/>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E134" s="3" t="inlineStr"/>
       <c r="F134" s="3" t="inlineStr"/>
       <c r="G134" s="3" t="inlineStr"/>
@@ -5090,7 +5278,11 @@
           <t>Hope you are not scared!</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr"/>
       <c r="G135" s="3" t="inlineStr"/>
@@ -5120,7 +5312,11 @@
           <t>Im cool ta luv but v.tired 2 cause i have been doin loads of planning all wk, we have got our social services inspection at the nursery! Take care &amp; spk sn x.</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr"/>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3" t="inlineStr"/>
       <c r="G136" s="3" t="inlineStr"/>
@@ -5192,7 +5388,11 @@
           <t>Sorry light turned green, I meant another friend wanted  &amp;lt;#&amp;gt;  worth but he may not be around</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr"/>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E138" s="3" t="inlineStr"/>
       <c r="F138" s="3" t="inlineStr"/>
       <c r="G138" s="3" t="inlineStr"/>
@@ -5222,7 +5422,11 @@
           <t>I got it before the new year cos yetunde said she wanted to surprise you with it but when i didnt see money i returned it mid january before the  &amp;lt;#&amp;gt; day return period ended.</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr"/>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr"/>
       <c r="G139" s="3" t="inlineStr"/>
@@ -5252,7 +5456,11 @@
           <t>Then why you came to hostel.</t>
         </is>
       </c>
-      <c r="D140" s="3" t="inlineStr"/>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E140" s="3" t="inlineStr"/>
       <c r="F140" s="3" t="inlineStr"/>
       <c r="G140" s="3" t="inlineStr"/>
@@ -5282,7 +5490,11 @@
           <t>Yeah like if it goes like it did with my friends imma flip my shit in like half an hour</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr"/>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr"/>
       <c r="G141" s="3" t="inlineStr"/>
@@ -5312,7 +5524,11 @@
           <t>The new deus ex game comin early next yr</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr"/>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E142" s="3" t="inlineStr"/>
       <c r="F142" s="3" t="inlineStr"/>
       <c r="G142" s="3" t="inlineStr"/>
@@ -5418,7 +5634,11 @@
           <t>Yes:)sura in sun tv.:)lol.</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr"/>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr"/>
       <c r="G145" s="3" t="inlineStr"/>
@@ -5448,7 +5668,11 @@
           <t>HI ITS JESS I DONT KNOW IF YOU ARE AT WORK BUT CALL ME WHEN U CAN IM AT HOME ALL EVE. XXX</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr"/>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E146" s="3" t="inlineStr"/>
       <c r="F146" s="3" t="inlineStr"/>
       <c r="G146" s="3" t="inlineStr"/>
@@ -5478,7 +5702,11 @@
           <t>Short But Cute : " Be a good person , but dont try to prove" ..... Gud mrng...</t>
         </is>
       </c>
-      <c r="D147" s="3" t="inlineStr"/>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr"/>
       <c r="G147" s="3" t="inlineStr"/>
@@ -5508,7 +5736,11 @@
           <t>Nope. Since ayo travelled, he has forgotten his guy</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr"/>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E148" s="3" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr"/>
       <c r="G148" s="3" t="inlineStr"/>
@@ -5538,7 +5770,11 @@
           <t>TaKe CaRE n gET WeLL sOOn</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr"/>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr"/>
       <c r="G149" s="3" t="inlineStr"/>
@@ -5610,7 +5846,11 @@
           <t>Ok lor...</t>
         </is>
       </c>
-      <c r="D151" s="3" t="inlineStr"/>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr"/>
@@ -5640,7 +5880,11 @@
           <t>No no:)this is kallis home ground.amla home town is durban:)</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr"/>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E152" s="3" t="inlineStr"/>
       <c r="F152" s="3" t="inlineStr"/>
       <c r="G152" s="3" t="inlineStr"/>
@@ -5670,7 +5914,11 @@
           <t>Like a personal sized or what</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr"/>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr"/>
       <c r="G153" s="3" t="inlineStr"/>
@@ -5700,7 +5948,11 @@
           <t>For real when u getting on yo? I only need 2 more tickets and one more jacket and I'm done. I already used all my multis.</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr"/>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E154" s="3" t="inlineStr"/>
       <c r="F154" s="3" t="inlineStr"/>
       <c r="G154" s="3" t="inlineStr"/>
@@ -5764,7 +6016,11 @@
           <t>Yes, princess. Are you going to make me moan?</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr"/>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E156" s="3" t="inlineStr"/>
       <c r="F156" s="3" t="inlineStr"/>
       <c r="G156" s="3" t="inlineStr"/>
@@ -5794,7 +6050,11 @@
           <t>U reach orchard already? U wan 2 go buy tickets first?</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr"/>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr"/>
       <c r="G157" s="3" t="inlineStr"/>
@@ -5824,7 +6084,11 @@
           <t>And several to you sir.</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr"/>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E158" s="3" t="inlineStr"/>
       <c r="F158" s="3" t="inlineStr"/>
       <c r="G158" s="3" t="inlineStr"/>
@@ -5934,7 +6198,11 @@
           <t>I am real, baby! I want to bring out your inner tigress...</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr"/>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr"/>
       <c r="G161" s="3" t="inlineStr"/>
@@ -6006,7 +6274,11 @@
           <t>Shall i ask one thing if you dont mistake me.</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr"/>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr"/>
       <c r="G163" s="3" t="inlineStr"/>
@@ -6070,7 +6342,11 @@
           <t>I got your back! Do you have any dislikes in bed?</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr"/>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr"/>
       <c r="G165" s="3" t="inlineStr"/>
@@ -6100,7 +6376,11 @@
           <t>I'm going out to buy mum's present ar.</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr"/>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E166" s="3" t="inlineStr"/>
       <c r="F166" s="3" t="inlineStr"/>
       <c r="G166" s="3" t="inlineStr"/>
@@ -6168,7 +6448,11 @@
           <t>Dear,Me at cherthala.in case u r coming cochin pls call bfore u start.i shall also reach accordingly.or tell me which day u r coming.tmorow i am engaged ans its holiday.</t>
         </is>
       </c>
-      <c r="D168" s="3" t="inlineStr"/>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E168" s="3" t="inlineStr"/>
       <c r="F168" s="3" t="inlineStr"/>
       <c r="G168" s="3" t="inlineStr"/>
@@ -6198,7 +6482,11 @@
           <t>Happy new year to u too!</t>
         </is>
       </c>
-      <c r="D169" s="3" t="inlineStr"/>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr"/>
       <c r="G169" s="3" t="inlineStr"/>
@@ -6228,7 +6516,11 @@
           <t>Mmm thats better now i got a roast down me! id b better if i had a few drinks down me 2! Good indian?</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr"/>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E170" s="3" t="inlineStr"/>
       <c r="F170" s="3" t="inlineStr"/>
       <c r="G170" s="3" t="inlineStr"/>
@@ -6258,7 +6550,11 @@
           <t>Wat uniform? In where get?</t>
         </is>
       </c>
-      <c r="D171" s="3" t="inlineStr"/>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E171" s="3" t="inlineStr"/>
       <c r="F171" s="3" t="inlineStr"/>
       <c r="G171" s="3" t="inlineStr"/>
@@ -6288,7 +6584,11 @@
           <t>When should I come over?</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr"/>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E172" s="3" t="inlineStr"/>
       <c r="F172" s="3" t="inlineStr"/>
       <c r="G172" s="3" t="inlineStr"/>
@@ -6360,7 +6660,11 @@
           <t>Sorry, I can't help you on this.</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr"/>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E174" s="3" t="inlineStr"/>
       <c r="F174" s="3" t="inlineStr"/>
       <c r="G174" s="3" t="inlineStr"/>
@@ -6390,7 +6694,11 @@
           <t>Unlimited texts. Limited minutes.</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr"/>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E175" s="3" t="inlineStr"/>
       <c r="F175" s="3" t="inlineStr"/>
       <c r="G175" s="3" t="inlineStr"/>
@@ -6420,7 +6728,11 @@
           <t>I keep ten rs in my shelf:) buy two egg.</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr"/>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E176" s="3" t="inlineStr"/>
       <c r="F176" s="3" t="inlineStr"/>
       <c r="G176" s="3" t="inlineStr"/>
@@ -6484,7 +6796,11 @@
           <t>Does not operate after  &amp;lt;#&amp;gt;  or what</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr"/>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E178" s="3" t="inlineStr"/>
       <c r="F178" s="3" t="inlineStr"/>
       <c r="G178" s="3" t="inlineStr"/>
@@ -6514,7 +6830,11 @@
           <t>hi baby im cruisin with my girl friend what r u up 2? give me a call in and hour at home if thats alright or fone me on this fone now love jenny xxx</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr"/>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E179" s="3" t="inlineStr"/>
       <c r="F179" s="3" t="inlineStr"/>
       <c r="G179" s="3" t="inlineStr"/>
@@ -6654,7 +6974,11 @@
           <t>I have a rather prominent bite mark on my right cheek</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr"/>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E183" s="3" t="inlineStr"/>
       <c r="F183" s="3" t="inlineStr"/>
       <c r="G183" s="3" t="inlineStr"/>
@@ -6684,7 +7008,11 @@
           <t>I plane to give on this month end.</t>
         </is>
       </c>
-      <c r="D184" s="3" t="inlineStr"/>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E184" s="3" t="inlineStr"/>
       <c r="F184" s="3" t="inlineStr"/>
       <c r="G184" s="3" t="inlineStr"/>
@@ -6714,7 +7042,11 @@
           <t>I love working from home :)</t>
         </is>
       </c>
-      <c r="D185" s="3" t="inlineStr"/>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E185" s="3" t="inlineStr"/>
       <c r="F185" s="3" t="inlineStr"/>
       <c r="G185" s="3" t="inlineStr"/>
@@ -6744,7 +7076,11 @@
           <t>Yes I posted a couple of pics on fb. There's still snow outside too. I'm just waking up :)</t>
         </is>
       </c>
-      <c r="D186" s="3" t="inlineStr"/>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E186" s="3" t="inlineStr"/>
       <c r="F186" s="3" t="inlineStr"/>
       <c r="G186" s="3" t="inlineStr"/>
@@ -6774,7 +7110,11 @@
           <t>PLEASSSSSSSEEEEEE TEL ME V AVENT DONE SPORTSx</t>
         </is>
       </c>
-      <c r="D187" s="3" t="inlineStr"/>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E187" s="3" t="inlineStr"/>
       <c r="F187" s="3" t="inlineStr"/>
       <c r="G187" s="3" t="inlineStr"/>
@@ -6846,7 +7186,11 @@
           <t>Need a coffee run tomo?Can't believe it's that time of week already</t>
         </is>
       </c>
-      <c r="D189" s="3" t="inlineStr"/>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E189" s="3" t="inlineStr"/>
       <c r="F189" s="3" t="inlineStr"/>
       <c r="G189" s="3" t="inlineStr"/>
@@ -6918,7 +7262,11 @@
           <t>In that case I guess I'll see you at campus lodge</t>
         </is>
       </c>
-      <c r="D191" s="3" t="inlineStr"/>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E191" s="3" t="inlineStr"/>
       <c r="F191" s="3" t="inlineStr"/>
       <c r="G191" s="3" t="inlineStr"/>
@@ -7054,7 +7402,11 @@
           <t>Mmmm.... I cant wait to lick it!</t>
         </is>
       </c>
-      <c r="D195" s="3" t="inlineStr"/>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3" t="inlineStr"/>
       <c r="G195" s="3" t="inlineStr"/>
@@ -7118,7 +7470,11 @@
           <t>"Speak only when you feel your words are better than the silence..." Gud mrng:-)</t>
         </is>
       </c>
-      <c r="D197" s="3" t="inlineStr"/>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E197" s="3" t="inlineStr"/>
       <c r="F197" s="3" t="inlineStr"/>
       <c r="G197" s="3" t="inlineStr"/>
@@ -7236,7 +7592,11 @@
           <t>Lmao!nice 1</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr"/>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E200" s="3" t="inlineStr"/>
       <c r="F200" s="3" t="inlineStr"/>
       <c r="G200" s="3" t="inlineStr"/>
@@ -7304,7 +7664,11 @@
           <t>Good. Good job. I like entrepreneurs</t>
         </is>
       </c>
-      <c r="D202" s="3" t="inlineStr"/>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E202" s="3" t="inlineStr"/>
       <c r="F202" s="3" t="inlineStr"/>
       <c r="G202" s="3" t="inlineStr"/>
@@ -7334,7 +7698,11 @@
           <t>You are always putting your business out there. You put pictures of your ass on facebook. You are one of the most open people i've ever met. Why would i think a picture of your room would hurt you, make you feel violated.</t>
         </is>
       </c>
-      <c r="D203" s="3" t="inlineStr"/>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E203" s="3" t="inlineStr"/>
       <c r="F203" s="3" t="inlineStr"/>
       <c r="G203" s="3" t="inlineStr"/>
@@ -7364,7 +7732,11 @@
           <t>Wrong phone! This phone! I answer this one but assume the other is people i don't well</t>
         </is>
       </c>
-      <c r="D204" s="3" t="inlineStr"/>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E204" s="3" t="inlineStr"/>
       <c r="F204" s="3" t="inlineStr"/>
       <c r="G204" s="3" t="inlineStr"/>
@@ -7394,7 +7766,11 @@
           <t>They r giving a second chance to rahul dengra.</t>
         </is>
       </c>
-      <c r="D205" s="3" t="inlineStr"/>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E205" s="3" t="inlineStr"/>
       <c r="F205" s="3" t="inlineStr"/>
       <c r="G205" s="3" t="inlineStr"/>
@@ -7466,7 +7842,11 @@
           <t>Have you always been saying welp?</t>
         </is>
       </c>
-      <c r="D207" s="3" t="inlineStr"/>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E207" s="3" t="inlineStr"/>
       <c r="F207" s="3" t="inlineStr"/>
       <c r="G207" s="3" t="inlineStr"/>
@@ -7530,7 +7910,11 @@
           <t>Lol your right. What diet? Everyday I cheat anyway. I'm meant to be a fatty :(</t>
         </is>
       </c>
-      <c r="D209" s="3" t="inlineStr"/>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E209" s="3" t="inlineStr"/>
       <c r="F209" s="3" t="inlineStr"/>
       <c r="G209" s="3" t="inlineStr"/>
@@ -7560,7 +7944,11 @@
           <t>I'm at work. Please call</t>
         </is>
       </c>
-      <c r="D210" s="3" t="inlineStr"/>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E210" s="3" t="inlineStr"/>
       <c r="F210" s="3" t="inlineStr"/>
       <c r="G210" s="3" t="inlineStr"/>
@@ -7628,7 +8016,11 @@
           <t>Have you laid your airtel line to rest?</t>
         </is>
       </c>
-      <c r="D212" s="3" t="inlineStr"/>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E212" s="3" t="inlineStr"/>
       <c r="F212" s="3" t="inlineStr"/>
       <c r="G212" s="3" t="inlineStr"/>
@@ -7658,7 +8050,11 @@
           <t>If you were/are free i can give. Otherwise nalla adi entey nattil kittum</t>
         </is>
       </c>
-      <c r="D213" s="3" t="inlineStr"/>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E213" s="3" t="inlineStr"/>
       <c r="F213" s="3" t="inlineStr"/>
       <c r="G213" s="3" t="inlineStr"/>
@@ -7734,7 +8130,11 @@
           <t>You still around? I could use a half-8th</t>
         </is>
       </c>
-      <c r="D215" s="3" t="inlineStr"/>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E215" s="3" t="inlineStr"/>
       <c r="F215" s="3" t="inlineStr"/>
       <c r="G215" s="3" t="inlineStr"/>
@@ -7764,7 +8164,11 @@
           <t>God bless.get good sleep my dear...i will pray!</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr"/>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E216" s="3" t="inlineStr"/>
       <c r="F216" s="3" t="inlineStr"/>
       <c r="G216" s="3" t="inlineStr"/>
@@ -7794,7 +8198,11 @@
           <t>I wish u were here. I feel so alone</t>
         </is>
       </c>
-      <c r="D217" s="3" t="inlineStr"/>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E217" s="3" t="inlineStr"/>
       <c r="F217" s="3" t="inlineStr"/>
       <c r="G217" s="3" t="inlineStr"/>
@@ -7824,7 +8232,11 @@
           <t xml:space="preserve">So when you gonna get rimac access </t>
         </is>
       </c>
-      <c r="D218" s="3" t="inlineStr"/>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E218" s="3" t="inlineStr"/>
       <c r="F218" s="3" t="inlineStr"/>
       <c r="G218" s="3" t="inlineStr"/>
@@ -7854,7 +8266,11 @@
           <t>Team meeting moved to 3 PM tomorrow in Conference Room B. Please bring your updated project timelines.</t>
         </is>
       </c>
-      <c r="D219" s="3" t="inlineStr"/>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E219" s="3" t="inlineStr"/>
       <c r="F219" s="3" t="inlineStr"/>
       <c r="G219" s="3" t="inlineStr"/>
@@ -7884,7 +8300,11 @@
           <t>A cute thought for friendship: "Its not necessary to share every secret with ur close Frnd, but watever u shared should be true"....</t>
         </is>
       </c>
-      <c r="D220" s="3" t="inlineStr"/>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E220" s="3" t="inlineStr"/>
       <c r="F220" s="3" t="inlineStr"/>
       <c r="G220" s="3" t="inlineStr"/>
@@ -7914,7 +8334,11 @@
           <t>Ill be at yours in about 3 mins but look out for me</t>
         </is>
       </c>
-      <c r="D221" s="3" t="inlineStr"/>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E221" s="3" t="inlineStr"/>
       <c r="F221" s="3" t="inlineStr"/>
       <c r="G221" s="3" t="inlineStr"/>
@@ -7944,7 +8368,11 @@
           <t>I want to show you the world, princess :) how about europe?</t>
         </is>
       </c>
-      <c r="D222" s="3" t="inlineStr"/>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E222" s="3" t="inlineStr"/>
       <c r="F222" s="3" t="inlineStr"/>
       <c r="G222" s="3" t="inlineStr"/>
@@ -7974,7 +8402,11 @@
           <t>Sitting ard nothing to do lor. U leh busy w work?</t>
         </is>
       </c>
-      <c r="D223" s="3" t="inlineStr"/>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E223" s="3" t="inlineStr"/>
       <c r="F223" s="3" t="inlineStr"/>
       <c r="G223" s="3" t="inlineStr"/>
@@ -8004,7 +8436,11 @@
           <t>Oh unintentionally not bad timing. Great. Fingers  the trains play along! Will give fifteen min warning.</t>
         </is>
       </c>
-      <c r="D224" s="3" t="inlineStr"/>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E224" s="3" t="inlineStr"/>
       <c r="F224" s="3" t="inlineStr"/>
       <c r="G224" s="3" t="inlineStr"/>
@@ -8068,7 +8504,11 @@
           <t>Pls clarify back if an open return ticket that i have can be preponed for me to go back to kerala.</t>
         </is>
       </c>
-      <c r="D226" s="3" t="inlineStr"/>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E226" s="3" t="inlineStr"/>
       <c r="F226" s="3" t="inlineStr"/>
       <c r="G226" s="3" t="inlineStr"/>
@@ -8098,7 +8538,11 @@
           <t>meet you in corporation st outside gap … you can see how my mind is working!</t>
         </is>
       </c>
-      <c r="D227" s="3" t="inlineStr"/>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E227" s="3" t="inlineStr"/>
       <c r="F227" s="3" t="inlineStr"/>
       <c r="G227" s="3" t="inlineStr"/>
@@ -8128,7 +8572,11 @@
           <t>I'm at home n ready...</t>
         </is>
       </c>
-      <c r="D228" s="3" t="inlineStr"/>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E228" s="3" t="inlineStr"/>
       <c r="F228" s="3" t="inlineStr"/>
       <c r="G228" s="3" t="inlineStr"/>
@@ -8158,7 +8606,11 @@
           <t>Where are the garage keys? They aren't on the bookshelf</t>
         </is>
       </c>
-      <c r="D229" s="3" t="inlineStr"/>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E229" s="3" t="inlineStr"/>
       <c r="F229" s="3" t="inlineStr"/>
       <c r="G229" s="3" t="inlineStr"/>
@@ -8382,7 +8834,11 @@
           <t>Is it your yahoo boys that bring in the perf? Or legal.</t>
         </is>
       </c>
-      <c r="D235" s="3" t="inlineStr"/>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E235" s="3" t="inlineStr"/>
       <c r="F235" s="3" t="inlineStr"/>
       <c r="G235" s="3" t="inlineStr"/>
@@ -8412,7 +8868,11 @@
           <t>No rushing. I'm not working. I'm in school so if we rush we go hungry.</t>
         </is>
       </c>
-      <c r="D236" s="3" t="inlineStr"/>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E236" s="3" t="inlineStr"/>
       <c r="F236" s="3" t="inlineStr"/>
       <c r="G236" s="3" t="inlineStr"/>
@@ -8484,7 +8944,11 @@
           <t>Oh, then your phone phoned me but it disconnected</t>
         </is>
       </c>
-      <c r="D238" s="3" t="inlineStr"/>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E238" s="3" t="inlineStr"/>
       <c r="F238" s="3" t="inlineStr"/>
       <c r="G238" s="3" t="inlineStr"/>
@@ -8514,7 +8978,11 @@
           <t>Headin towards busetop</t>
         </is>
       </c>
-      <c r="D239" s="3" t="inlineStr"/>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E239" s="3" t="inlineStr"/>
       <c r="F239" s="3" t="inlineStr"/>
       <c r="G239" s="3" t="inlineStr"/>
@@ -8544,7 +9012,11 @@
           <t>I'm turning off my phone. My moms telling everyone I have cancer. And my sister won't stop calling. It hurts to talk. Can't put up with it. See u when u get home. Love u</t>
         </is>
       </c>
-      <c r="D240" s="3" t="inlineStr"/>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E240" s="3" t="inlineStr"/>
       <c r="F240" s="3" t="inlineStr"/>
       <c r="G240" s="3" t="inlineStr"/>
@@ -8650,7 +9122,11 @@
           <t>I jokin oni lar.. Ü busy then i wun disturb ü.</t>
         </is>
       </c>
-      <c r="D243" s="3" t="inlineStr"/>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E243" s="3" t="inlineStr"/>
       <c r="F243" s="3" t="inlineStr"/>
       <c r="G243" s="3" t="inlineStr"/>
@@ -8752,7 +9228,11 @@
           <t>I.ll hand her my phone to chat wit u</t>
         </is>
       </c>
-      <c r="D246" s="3" t="inlineStr"/>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E246" s="3" t="inlineStr"/>
       <c r="F246" s="3" t="inlineStr"/>
       <c r="G246" s="3" t="inlineStr"/>
@@ -8782,7 +9262,11 @@
           <t xml:space="preserve">That's the trouble with classes that go well - you're due a dodgey one … Expecting mine tomo! See you for recovery, same time, same place </t>
         </is>
       </c>
-      <c r="D247" s="3" t="inlineStr"/>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E247" s="3" t="inlineStr"/>
       <c r="F247" s="3" t="inlineStr"/>
       <c r="G247" s="3" t="inlineStr"/>
@@ -8812,7 +9296,11 @@
           <t>Check with nuerologist.</t>
         </is>
       </c>
-      <c r="D248" s="3" t="inlineStr"/>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E248" s="3" t="inlineStr"/>
       <c r="F248" s="3" t="inlineStr"/>
       <c r="G248" s="3" t="inlineStr"/>
@@ -8926,7 +9414,11 @@
           <t>Love it! The girls at the office may wonder why you are smiling but sore...</t>
         </is>
       </c>
-      <c r="D251" s="3" t="inlineStr"/>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="E251" s="3" t="inlineStr"/>
       <c r="F251" s="3" t="inlineStr"/>
       <c r="G251" s="3" t="inlineStr"/>
